--- a/data/trans_dic/IP24_R2_2023-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP24_R2_2023-Habitat-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>19,47%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>20,64%</t>
+          <t>13,25%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>17,96%</t>
+          <t>16,42%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>10,25; 20,34</t>
+          <t>11,66; 36,02</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>12,14; 41,45</t>
+          <t>9,16; 18,43</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>13,08; 28,78</t>
+          <t>12,02; 26,38</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>21,02%</t>
+          <t>13,79%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>16,31%</t>
+          <t>16,83%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>18,33%</t>
+          <t>15,12%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>15,14; 29,22</t>
+          <t>10,15; 17,65</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>12,52; 20,77</t>
+          <t>12,83; 21,72</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15,38; 22,79</t>
+          <t>12,51; 18,03</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>35,03%</t>
+          <t>21,0%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>22,62%</t>
+          <t>23,05%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>28,94%</t>
+          <t>21,99%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>21,89; 62,25</t>
+          <t>15,72; 27,54</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>16,94; 29,4</t>
+          <t>17,33; 29,78</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>21,87; 43,91</t>
+          <t>18,1; 26,71</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>18,99%</t>
+          <t>13,82%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>17,49%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>15,64%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>13,58; 24,88</t>
+          <t>10,13; 18,68</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>9,6; 18,6</t>
+          <t>13,07; 22,58</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>12,73; 19,78</t>
+          <t>12,56; 19,01</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>23,41%</t>
+          <t>16,54%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>17,86%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>17,17%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>18,78; 34,54</t>
+          <t>14,19; 20,76</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>15,28; 22,23</t>
+          <t>15,46; 20,49</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>17,68; 25,51</t>
+          <t>15,43; 19,39</t>
         </is>
       </c>
     </row>
@@ -831,12 +831,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -884,12 +884,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>34</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>17241</t>
+          <t>24438</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>28872</t>
+          <t>15997</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>46113</t>
+          <t>40435</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>11984; 23781</t>
+          <t>14630; 45206</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>16986; 57988</t>
+          <t>11061; 22252</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>33582; 73915</t>
+          <t>29604; 64964</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>53</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>68</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -980,17 +980,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>40049</t>
+          <t>32536</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>41390</t>
+          <t>31033</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>81439</t>
+          <t>63569</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>28850; 55665</t>
+          <t>23939; 41649</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>31770; 52693</t>
+          <t>23668; 40051</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>68299; 101247</t>
+          <t>52589; 75791</t>
         </is>
       </c>
     </row>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>54</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1053,17 +1053,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>66418</t>
+          <t>34957</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>41357</t>
+          <t>36000</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>107775</t>
+          <t>70957</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>41509; 118019</t>
+          <t>26161; 45846</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>30984; 53759</t>
+          <t>27071; 46523</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>81443; 163562</t>
+          <t>58404; 86164</t>
         </is>
       </c>
     </row>
@@ -1103,12 +1103,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>44</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1126,17 +1126,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>31687</t>
+          <t>23414</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>23882</t>
+          <t>29057</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>55569</t>
+          <t>52470</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>22664; 41509</t>
+          <t>17151; 31636</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>17407; 33705</t>
+          <t>21724; 37514</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>44310; 68836</t>
+          <t>42158; 63790</t>
         </is>
       </c>
     </row>
@@ -1176,12 +1176,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>186</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>185</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>186</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1199,17 +1199,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>155395</t>
+          <t>115344</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>135501</t>
+          <t>112087</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>290896</t>
+          <t>227431</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>124635; 229313</t>
+          <t>98906; 144738</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>115769; 168429</t>
+          <t>97037; 128550</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>251372; 362673</t>
+          <t>204352; 256861</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP24_R2_2023-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP24_R2_2023-Habitat-trans_dic.xlsx
@@ -17,7 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -98,7 +100,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -111,6 +113,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -477,341 +485,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Menores que no realizan actividad física en su tiempo libre (o no tienen tiempo libre) (tasa de respuesta: 99,43%)</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niña</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="n"/>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" hidden="1">
-      <c r="A3" s="4" t="n"/>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>&lt;10.000 hab</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>19,47%</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>13,25%</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>16,42%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n"/>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>11,66; 36,02</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>9,16; 18,43</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>12,02; 26,38</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>10-50.000 hab</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>13,79%</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>16,83%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>15,12%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>10,15; 17,65</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>12,83; 21,72</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>12,51; 18,03</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>&gt;50.000 hab</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>21,0%</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>23,05%</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>21,99%</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n"/>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>15,72; 27,54</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>17,33; 29,78</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>18,1; 26,71</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>Capitales</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>13,82%</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>17,49%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>15,64%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n"/>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>10,13; 18,68</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>13,07; 22,58</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>12,56; 19,01</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>16,54%</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>17,86%</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>17,17%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>14,19; 20,76</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>15,46; 20,49</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>15,43; 19,39</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -879,69 +552,51 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>0.1947437419052585</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0.1324874325778719</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0.1642150776268776</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>24438</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>15997</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>40435</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>0.1165867620317805</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>0.09160627955488554</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>0.1202276289687162</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>14630; 45206</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>11061; 22252</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>29604; 64964</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>0.3602430961738931</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>0.1842899516270266</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>0.2638294826453997</v>
       </c>
     </row>
     <row r="7">
@@ -952,69 +607,51 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>121</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>0.1379086133129708</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0.1682802415057558</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.1512335273989766</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>32536</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>31033</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>63569</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>0.1014690593584778</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>0.1283428283838275</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>0.125111783135027</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>23939; 41649</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>23668; 40051</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>52589; 75791</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>0.1765359422004884</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>0.2171815274700691</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>0.1803106513667997</v>
       </c>
     </row>
     <row r="10">
@@ -1025,69 +662,51 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>106</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>0.2100238312893654</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.2304675838507961</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.2199213164632432</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>34957</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>36000</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>70957</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>0.1571750340426178</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>0.1733074560207495</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>0.1810166018657724</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>26161; 45846</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>27071; 46523</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>58404; 86164</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0.27544614305538</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>0.2978332592662614</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0.2670527803233207</v>
       </c>
     </row>
     <row r="13">
@@ -1098,69 +717,51 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0.1382349779701956</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0.1748706546580359</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.156377229482372</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>23414</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>29057</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>52470</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>0.1012587848069635</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>0.1307441458014936</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>0.1256444703002192</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>17151; 31636</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>21724; 37514</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>42158; 63790</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0.1867770604767594</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>0.2257728947924311</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>0.1901122759440579</v>
       </c>
     </row>
     <row r="16">
@@ -1171,69 +772,51 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>186</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>185</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>371</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>0.1654325638349483</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>0.1786179812462261</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>0.1716783750878262</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>115344</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>112087</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>227431</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>0.1418564869991527</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>0.1546355700538772</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>0.1542568263708933</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>98906; 144738</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>97037; 128550</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>204352; 256861</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>0.2075912977329456</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>0.2048541522789729</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>0.1938942446019938</v>
       </c>
     </row>
     <row r="19">
@@ -1254,4 +837,449 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que no realizan actividad física en su tiempo libre (o no tienen tiempo libre) (tasa de respuesta: 99,43%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>&lt;10.000 hab</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>29</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>34</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>24438</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>15997</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>40435</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>14630</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>11061</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>29604</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n"/>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>45206</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>22252</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>64964</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>10-50.000 hab</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>68</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>53</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>32536</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>31033</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>63569</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n"/>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>23939</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>23668</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>52589</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>41649</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>40051</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>75791</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>&gt;50.000 hab</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>52</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>54</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n"/>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>34957</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>36000</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>70957</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>26161</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>27071</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>58404</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>45846</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>46523</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>86164</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>37</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>44</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>23414</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>29057</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>52470</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>17151</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>21724</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>42158</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n"/>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>31636</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>37514</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>63790</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="n">
+        <v>186</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>185</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="n">
+        <v>115344</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>112087</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>227431</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n"/>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="n">
+        <v>98906</v>
+      </c>
+      <c r="D22" s="6" t="n">
+        <v>97037</v>
+      </c>
+      <c r="E22" s="6" t="n">
+        <v>204352</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="n">
+        <v>144738</v>
+      </c>
+      <c r="D23" s="6" t="n">
+        <v>128550</v>
+      </c>
+      <c r="E23" s="6" t="n">
+        <v>256861</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A20:A23"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A16:A19"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>